--- a/w5-zone3-consumption-gating/poc08/POC08_Control_Table_Tags_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc08/POC08_Control_Table_Tags_Tracker.xlsx
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -724,71 +724,71 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>You must be able to USE ROLE both SECURITYADMIN and SYSADMIN. ACCOUNTADMIN is NOT required. Every grant on the shared database and warehouse is issued by SECURITYADMIN, which can grant on objects it does not own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+          <t>You must be able to USE ROLE both SECURITYADMIN and SYSADMIN. Every grant on the shared database and warehouse is issued by SECURITYADMIN, which can grant on objects it does not own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>One account-level grant</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>GRANT APPLY MASKING POLICY ON ACCOUNT TO ROLE P8_GOV_ROLE;  —  the only thing in the pack not scoped to LM_POC_DB. Attaching a masking policy to a TAG needs it; owning the tag and the policy is NOT enough. SECURITYADMIN can normally issue it via MANAGE GRANTS; if your account refuses, run that one line as ACCOUNTADMIN. Nothing else needs that role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>FINDING to carry into the write-up</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Tag-based masking requires an ACCOUNT-WIDE privilege for whoever attaches policies to tags. That makes the governance role powerful, and the grant a decision rather than a formality. The PIPELINE does not need it: P8_BATCH only SETS tags, which needs APPLY on the tag alone. Found by running 00_setup.sql, not by reading it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>RESULT TALLY — fill in as you run</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Test cases</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Fail / not run</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>S0  Day 0 — deployment</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>S1  Day 1 — first publish</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>S2  Day 2 — governance change</t>
+          <t>S0  Day 0 — deployment</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr"/>
@@ -796,7 +796,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>S3  Fail closed</t>
+          <t>S1  Day 1 — first publish</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
@@ -806,19 +806,43 @@
       <c r="D18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>S2  Day 2 — governance change</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>S3  Fail closed</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B21" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="9" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B11:D11"/>
@@ -826,10 +850,12 @@
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1408,7 +1434,7 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>The only role that may write OBJECT_TAGS.</t>
+          <t>The only role that may write OBJECT_TAGS. Also holds APPLY MASKING POLICY ON ACCOUNT — required to attach a policy to a tag.</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1758,7 @@
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>Attached to P8_PII with FORCE, which is idempotent on a re-run.</t>
+          <t>Attached to P8_PII with FORCE, which is idempotent on a re-run. The attach needs APPLY MASKING POLICY ON ACCOUNT — ownership alone is not enough.</t>
         </is>
       </c>
     </row>

--- a/w5-zone3-consumption-gating/poc08/POC08_Control_Table_Tags_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc08/POC08_Control_Table_Tags_Tracker.xlsx
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -743,7 +743,7 @@
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FINDING to carry into the write-up</t>
+          <t>FINDING 1 - tag masking needs an account privilege</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -752,55 +752,55 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>FINDING 2 - the swap moves grants</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ALTER SCHEMA P8_STG SWAP WITH P8_LIVE exchanges the two schemas TOGETHER WITH THEIR GRANTS. A grant issued against the name P8_STG follows the object, which after one swap is called P8_LIVE. So a grant on ONE half works on day 1 and is gone on day 2. THE RULE: in a swap-pair design every schema-level grant, FUTURE grants included, goes on BOTH schemas. This is the schema-level form of the storage alternation that governs the whole approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>RESULT TALLY — fill in as you run</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Test cases</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Fail / not run</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>S0  Day 0 — deployment</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>S1  Day 1 — first publish</t>
+          <t>S0  Day 0 — deployment</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr"/>
@@ -808,7 +808,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>S2  Day 2 — governance change</t>
+          <t>S1  Day 1 — first publish</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
@@ -820,7 +820,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>S3  Fail closed</t>
+          <t>S2  Day 2 — governance change</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
@@ -830,29 +830,42 @@
       <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>S3  Fail closed</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B22" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="9" t="inlineStr"/>
-      <c r="D21" s="9" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B14:D14"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>

--- a/w5-zone3-consumption-gating/poc08/POC08_Control_Table_Tags_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc08/POC08_Control_Table_Tags_Tracker.xlsx
@@ -3407,9 +3407,21 @@
       <c r="E3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS - re-capture</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S0 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Query ran, but the shot crops TABLES_FOUND so the 0 is not visible. Re-capture with the value column in frame; everything downstream is consistent with a clean day-0 start.</t>
+        </is>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
@@ -3427,9 +3439,21 @@
       <c r="E4" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S0 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 rows, EMAIL and SSN, both UPPERCASE, tag LM_POC_DB.P8_GOV.P8_PII.</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -3447,9 +3471,21 @@
       <c r="E5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S0 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P8_PII present, matching the tag TC-0.2 declares.</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -3467,9 +3503,21 @@
       <c r="E6" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S0 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 row: P8_MASK attached to P8_PII, REF_ENTITY_DOMAIN = TAG. Masking is live, so every later mask check means something.</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -3487,9 +3535,21 @@
       <c r="E7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S1 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Query produced no results" - the fresh build carries no tags. This is the mechanism that lets a later REMOVE work at all.</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
@@ -3507,9 +3567,21 @@
       <c r="E8" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S1 - 3 shots</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preview generated exactly 2 ALTERs; the block returned "tags applied: 2"; result is exactly EMAIL=EMAIL and SSN=SSN with no PHONE. Also confirms EXECUTE IMMEDIATE $$ runs correctly in Snowsight.</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -3527,9 +3599,21 @@
       <c r="E9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S1 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zero rows: nothing declared is untagged. Gate passes.</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
@@ -3547,9 +3631,21 @@
       <c r="E10" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S1 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email and ssn ***MASKED***, phone real. The tag is enforcing, not just present in metadata; phone in the clear is correct on day 1.</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -3567,9 +3663,21 @@
       <c r="E11" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S1 - 2 shots</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entitled reader: real values, batch_id B1. Unentitled: email and ssn masked, phone real, B1.</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
@@ -3587,9 +3695,21 @@
       <c r="E12" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S2 - 2 shots</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Declaration now EMAIL=EMAIL_ADDRESS and PHONE=PHONE, SSN gone; updated_by and reason populated. Batch B2 loaded, 20 rows.</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -3607,9 +3727,21 @@
       <c r="E13" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S2 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zero rows on the OTHER storage too - nobody ever tagged it and the build inherits nothing.</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -3627,9 +3759,21 @@
       <c r="E14" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S2 - 2 shots</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEADLINE RESULT. EMAIL -&gt; EMAIL_ADDRESS (changed), PHONE -&gt; PHONE (added), and NO SSN row (removed). One control-row edit delivered all three kinds of change.</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -3647,9 +3791,21 @@
       <c r="E15" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S2 - 2 shots</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gate zero rows. Reader sees email MASKED, phone MASKED, ssn REAL - the exact inverse of day 1. The removal is ENFORCED, not just metadata.</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
@@ -3667,9 +3823,21 @@
       <c r="E16" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S2 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Through the unchanged thin view: batch_id B2, email and phone masked, ssn real. The readers object name never moved.</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
@@ -3687,9 +3855,21 @@
       <c r="E17" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S3 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">declarations = 0, verdict REFUSE. An undeclared object is never built.</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
@@ -3707,9 +3887,21 @@
       <c r="E18" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S3 - 3 shots</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validity gate returned tags_visible = 1, so the pipeline CAN read the tag list holding only APPLY - that open question is now answered. The comparison then returned P8_NOPE.</t>
+        </is>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
@@ -3727,9 +3919,21 @@
       <c r="E19" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S3 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One row, NOSUCHCOL. Declaration and data have diverged, so the publish refuses.</t>
+        </is>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
@@ -3747,9 +3951,21 @@
       <c r="E20" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S3 - 2 shots</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTER TABLE refused for want of APPLY, then the gate returned EMAIL. No swap happened.</t>
+        </is>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
@@ -3767,9 +3983,21 @@
       <c r="E21" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S3 - 1 shot</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UPDATE refused: P8_BATCH holds SELECT only. The pipeline cannot edit its own rulebook.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3941,6 +4169,11 @@
       <c r="C2" s="1" t="s">
         <v>141</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS - re-capture</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
@@ -3966,6 +4199,11 @@
       <c r="C27" s="10" t="s">
         <v>145</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
@@ -3991,6 +4229,11 @@
       <c r="C54" s="1" t="s">
         <v>149</v>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
@@ -4015,6 +4258,11 @@
       </c>
       <c r="C78" s="10" t="s">
         <v>153</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4055,6 +4303,11 @@
       <c r="C2" s="1" t="s">
         <v>157</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
@@ -4080,6 +4333,11 @@
       <c r="C38" s="10" t="s">
         <v>161</v>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
@@ -4105,6 +4363,11 @@
       <c r="C113" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
@@ -4130,6 +4393,11 @@
       <c r="C151" s="10" t="s">
         <v>169</v>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
@@ -4154,6 +4422,11 @@
       </c>
       <c r="C173" s="1" t="s">
         <v>173</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4194,6 +4467,11 @@
       <c r="C2" s="10" t="s">
         <v>177</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
@@ -4219,6 +4497,11 @@
       <c r="C54" s="1" t="s">
         <v>181</v>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
@@ -4244,6 +4527,11 @@
       <c r="C90" s="10" t="s">
         <v>185</v>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
@@ -4269,6 +4557,11 @@
       <c r="C142" s="1" t="s">
         <v>189</v>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
@@ -4293,6 +4586,11 @@
       </c>
       <c r="C199" s="10" t="s">
         <v>193</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4333,6 +4631,11 @@
       <c r="C2" s="9" t="s">
         <v>197</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
@@ -4358,6 +4661,11 @@
       <c r="C27" s="9" t="s">
         <v>201</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
@@ -4383,6 +4691,11 @@
       <c r="C86" s="9" t="s">
         <v>205</v>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
@@ -4408,6 +4721,11 @@
       <c r="C121" s="9" t="s">
         <v>209</v>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
@@ -4432,6 +4750,11 @@
       </c>
       <c r="C182" s="9" t="s">
         <v>213</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>
